--- a/temp_doc/STS SAS 25-25/SOAL AKL.xlsx
+++ b/temp_doc/STS SAS 25-25/SOAL AKL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/cbt2.0admin/temp_doc/STS SAS 25-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78B5673-B5C9-E543-AA54-37BAF3FCBC41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BF37AB-84B5-2A43-8A33-646F42CEFDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{099D4B89-C2CA-F649-A3F6-71778DCA3EA6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
   <si>
     <t>category</t>
   </si>
@@ -47,208 +47,112 @@
     <t>fullname</t>
   </si>
   <si>
-    <t>AGAMA ISLAM ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN PANCASILA ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN JASMANI, OLAHRAGA DAN KESEHATAN ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>SEJARAH ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>SENI DAN BUDAYA ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>MUATAN LOKAL ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>KODING DAN KECERDASAN ARTIFISIAL ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>INFORMATIKA ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>PROJEK ILMU PENGETAHUAN ALAM DAN SOSIAL ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>DASAR - DASAR PROGRAM KEAHLIAN ( X AKL 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN PANCASILA ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN JASMANI, OLAHRAGA DAN KESEHATAN ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>SEJARAH ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>SENI DAN BUDAYA ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>MUATAN LOKAL ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>KODING DAN KECERDASAN ARTIFISIAL ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>INFORMATIKA ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>PROJEK ILMU PENGETAHUAN ALAM DAN SOSIAL ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>DASAR - DASAR PROGRAM KEAHLIAN ( X AKL 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN PANCASILA ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN JASMANI, OLAHRAGA DAN KESEHATAN ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>PROJEK KREATIF DAN KEWIRAUSAHAAN ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>MUATAN LOKAL ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>MATA PELAJARAN PILIHAN ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>SEJARAH ( XI AKL 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN PANCASILA ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN JASMANI, OLAHRAGA DAN KESEHATAN ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>PROJEK KREATIF DAN KEWIRAUSAHAAN ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>MUATAN LOKAL ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>MATA PELAJARAN PILIHAN ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>MATEMATIKA ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>SEJARAH ( XI AKL 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XII AKL 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XII AKL 1 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN PANCASILA ( XII AKL 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( XII AKL 1 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XII AKL 1 )</t>
-  </si>
-  <si>
-    <t>PROJEK KREATIF DAN KEWIRAUSAHAAN ( XII AKL 1 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XII AKL 1 )</t>
-  </si>
-  <si>
-    <t>MATA PELAJARAN PILIHAN ( XII AKL 1 )</t>
-  </si>
-  <si>
-    <t>AGAMA ISLAM ( XII AKL 2 )</t>
-  </si>
-  <si>
-    <t>AGAMA KRISTEN ( XII AKL 2 )</t>
-  </si>
-  <si>
-    <t>PENDIDIKAN PANCASILA ( XII AKL 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INDONESIA ( XII AKL 2 )</t>
-  </si>
-  <si>
-    <t>BAHASA INGGRIS ( XII AKL 2 )</t>
-  </si>
-  <si>
-    <t>PROJEK KREATIF DAN KEWIRAUSAHAAN ( XII AKL 2 )</t>
-  </si>
-  <si>
-    <t>KONSENTRASI KEAHLIAN ( XII AKL 2 )</t>
-  </si>
-  <si>
-    <t>MATA PELAJARAN PILIHAN ( XII AKL 2 )</t>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII TJKT 1 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII TJKT 1 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII TJKT 1 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII TJKT 1 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII TJKT 2 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII TJKT 2 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII TJKT 2 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII TJKT 2 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII TJKT 3 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII TJKT 3 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII TJKT 3 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII TJKT 3 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII AKL 1 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII AKL 1 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII AKL 1 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII AKL 1 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII AKL 2 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII AKL 2 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII AKL 2 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII AKL 2 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII MPLB 1 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII MPLB 1 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII MPLB 1 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII MPLB 1 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII MPLB 2 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII MPLB 2 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII MPLB 2 )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII MPLB 2 )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII DKV )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII DKV )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII DKV )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII DKV )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - PILIHAN GANDA ( XII PM )</t>
+  </si>
+  <si>
+    <t>BAHASA JEPANG  - ESAI ( XII PM )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - PILIHAN GANDA ( XII PM )</t>
+  </si>
+  <si>
+    <t>KODING KECERDASAN ARTIFISIAL  - ESAI ( XII PM )</t>
   </si>
 </sst>
 </file>
@@ -642,11 +546,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6DDCBB2-F69E-B845-9F0C-79E2CD8D8A7A}">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="53.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -662,7 +566,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -673,7 +577,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -684,7 +588,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -695,7 +599,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -706,7 +610,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -717,7 +621,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -728,7 +632,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -739,7 +643,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -750,7 +654,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -761,7 +665,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -772,7 +676,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -783,7 +687,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -794,7 +698,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -805,7 +709,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
@@ -816,7 +720,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -827,7 +731,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
@@ -838,7 +742,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
@@ -849,7 +753,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
@@ -860,7 +764,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
@@ -871,7 +775,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
@@ -882,7 +786,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
@@ -893,7 +797,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
@@ -904,7 +808,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
@@ -915,7 +819,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
@@ -926,7 +830,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
@@ -937,7 +841,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
         <v>28</v>
@@ -948,7 +852,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
         <v>29</v>
@@ -959,7 +863,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
         <v>30</v>
@@ -970,7 +874,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
         <v>31</v>
@@ -981,7 +885,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
         <v>32</v>
@@ -992,7 +896,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
@@ -1003,7 +907,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
         <v>34</v>
@@ -1014,7 +918,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
         <v>35</v>
@@ -1025,7 +929,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B35" t="s">
         <v>36</v>
@@ -1036,7 +940,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
         <v>37</v>
@@ -1047,365 +951,13 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
       </c>
       <c r="C37" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38">
-        <v>18</v>
-      </c>
-      <c r="B38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39">
-        <v>18</v>
-      </c>
-      <c r="B39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40">
-        <v>18</v>
-      </c>
-      <c r="B40" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41">
-        <v>18</v>
-      </c>
-      <c r="B41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42">
-        <v>19</v>
-      </c>
-      <c r="B42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43">
-        <v>19</v>
-      </c>
-      <c r="B43" t="s">
-        <v>44</v>
-      </c>
-      <c r="C43" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44">
-        <v>19</v>
-      </c>
-      <c r="B44" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>19</v>
-      </c>
-      <c r="B45" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>19</v>
-      </c>
-      <c r="B46" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>19</v>
-      </c>
-      <c r="B47" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>19</v>
-      </c>
-      <c r="B48" t="s">
-        <v>49</v>
-      </c>
-      <c r="C48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>19</v>
-      </c>
-      <c r="B49" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>19</v>
-      </c>
-      <c r="B50" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>19</v>
-      </c>
-      <c r="B51" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52">
-        <v>19</v>
-      </c>
-      <c r="B52" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53">
-        <v>19</v>
-      </c>
-      <c r="B53" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54">
-        <v>20</v>
-      </c>
-      <c r="B54" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>20</v>
-      </c>
-      <c r="B55" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>20</v>
-      </c>
-      <c r="B56" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>20</v>
-      </c>
-      <c r="B57" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>20</v>
-      </c>
-      <c r="B58" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>20</v>
-      </c>
-      <c r="B59" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60">
-        <v>20</v>
-      </c>
-      <c r="B60" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61">
-        <v>20</v>
-      </c>
-      <c r="B61" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>21</v>
-      </c>
-      <c r="B62" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>21</v>
-      </c>
-      <c r="B63" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64">
-        <v>21</v>
-      </c>
-      <c r="B64" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65">
-        <v>21</v>
-      </c>
-      <c r="B65" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66">
-        <v>21</v>
-      </c>
-      <c r="B66" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67">
-        <v>21</v>
-      </c>
-      <c r="B67" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68">
-        <v>21</v>
-      </c>
-      <c r="B68" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>21</v>
-      </c>
-      <c r="B69" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
